--- a/prompt-coach/research/live-tests/fixtures/fr_trial_balance.xlsx
+++ b/prompt-coach/research/live-tests/fixtures/fr_trial_balance.xlsx
@@ -428,7 +428,7 @@
         <v>Deferred revenue</v>
       </c>
       <c r="B4">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5">
